--- a/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v1/앱/public/sample/가짜_거래내역_2026-08.xlsx
+++ b/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v1/앱/public/sample/가짜_거래내역_2026-08.xlsx
@@ -550,13 +550,13 @@
         <v>가나식품</v>
       </c>
       <c r="D9">
-        <v>2100000</v>
+        <v>1600000</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9">
-        <v>7190000</v>
+        <v>7690000</v>
       </c>
       <c r="G9" t="str">
         <v>가짜지점</v>
@@ -579,7 +579,7 @@
         <v/>
       </c>
       <c r="F10">
-        <v>6550000</v>
+        <v>7050000</v>
       </c>
       <c r="G10" t="str">
         <v>가짜지점</v>
@@ -602,7 +602,7 @@
         <v/>
       </c>
       <c r="F11">
-        <v>6050000</v>
+        <v>6550000</v>
       </c>
       <c r="G11" t="str">
         <v>가짜지점</v>
@@ -625,7 +625,7 @@
         <v>1650000</v>
       </c>
       <c r="F12">
-        <v>7700000</v>
+        <v>8200000</v>
       </c>
       <c r="G12" t="str">
         <v>가짜지점</v>
@@ -648,7 +648,7 @@
         <v>1600000</v>
       </c>
       <c r="F13">
-        <v>9300000</v>
+        <v>9800000</v>
       </c>
       <c r="G13" t="str">
         <v>가짜지점</v>
@@ -671,7 +671,7 @@
         <v/>
       </c>
       <c r="F14">
-        <v>8100000</v>
+        <v>8600000</v>
       </c>
       <c r="G14" t="str">
         <v>가짜지점</v>
@@ -694,7 +694,7 @@
         <v>430000</v>
       </c>
       <c r="F15">
-        <v>8530000</v>
+        <v>9030000</v>
       </c>
       <c r="G15" t="str">
         <v>가짜지점</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F16">
-        <v>8080000</v>
+        <v>8580000</v>
       </c>
       <c r="G16" t="str">
         <v>가짜지점</v>
@@ -740,7 +740,7 @@
         <v/>
       </c>
       <c r="F17">
-        <v>7996000</v>
+        <v>8496000</v>
       </c>
       <c r="G17" t="str">
         <v>가짜지점</v>
@@ -763,7 +763,7 @@
         <v>1900000</v>
       </c>
       <c r="F18">
-        <v>9896000</v>
+        <v>10396000</v>
       </c>
       <c r="G18" t="str">
         <v>가짜지점</v>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="F19">
-        <v>9016000</v>
+        <v>9516000</v>
       </c>
       <c r="G19" t="str">
         <v>가짜지점</v>
@@ -809,7 +809,7 @@
         <v>1000000</v>
       </c>
       <c r="F20">
-        <v>10016000</v>
+        <v>10516000</v>
       </c>
       <c r="G20" t="str">
         <v>가짜지점</v>
@@ -832,7 +832,7 @@
         <v/>
       </c>
       <c r="F21">
-        <v>9696000</v>
+        <v>10196000</v>
       </c>
       <c r="G21" t="str">
         <v>가짜지점</v>
@@ -855,7 +855,7 @@
         <v/>
       </c>
       <c r="F22">
-        <v>9521000</v>
+        <v>10021000</v>
       </c>
       <c r="G22" t="str">
         <v>가짜지점</v>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="F23">
-        <v>9356000</v>
+        <v>9856000</v>
       </c>
       <c r="G23" t="str">
         <v>가짜지점</v>
@@ -895,13 +895,13 @@
         <v>가나식품</v>
       </c>
       <c r="D24">
-        <v>1950000</v>
+        <v>1500000</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24">
-        <v>7406000</v>
+        <v>8356000</v>
       </c>
       <c r="G24" t="str">
         <v>가짜지점</v>
@@ -924,7 +924,7 @@
         <v/>
       </c>
       <c r="F25">
-        <v>7296000</v>
+        <v>8246000</v>
       </c>
       <c r="G25" t="str">
         <v>가짜지점</v>
@@ -947,7 +947,7 @@
         <v/>
       </c>
       <c r="F26">
-        <v>4496000</v>
+        <v>5446000</v>
       </c>
       <c r="G26" t="str">
         <v>가짜지점</v>
@@ -970,7 +970,7 @@
         <v/>
       </c>
       <c r="F27">
-        <v>2596000</v>
+        <v>3546000</v>
       </c>
       <c r="G27" t="str">
         <v>가짜지점</v>
@@ -993,7 +993,7 @@
         <v/>
       </c>
       <c r="F28">
-        <v>1776000</v>
+        <v>2726000</v>
       </c>
       <c r="G28" t="str">
         <v>가짜지점</v>
@@ -1016,7 +1016,7 @@
         <v/>
       </c>
       <c r="F29">
-        <v>1236000</v>
+        <v>2186000</v>
       </c>
       <c r="G29" t="str">
         <v>가짜지점</v>
@@ -1039,7 +1039,7 @@
         <v/>
       </c>
       <c r="F30">
-        <v>1166000</v>
+        <v>2116000</v>
       </c>
       <c r="G30" t="str">
         <v>가짜지점</v>
@@ -1062,7 +1062,7 @@
         <v>1580000</v>
       </c>
       <c r="F31">
-        <v>2746000</v>
+        <v>3696000</v>
       </c>
       <c r="G31" t="str">
         <v>가짜지점</v>
@@ -1085,7 +1085,7 @@
         <v>1640000</v>
       </c>
       <c r="F32">
-        <v>4386000</v>
+        <v>5336000</v>
       </c>
       <c r="G32" t="str">
         <v>가짜지점</v>
@@ -1108,7 +1108,7 @@
         <v/>
       </c>
       <c r="F33">
-        <v>4331000</v>
+        <v>5281000</v>
       </c>
       <c r="G33" t="str">
         <v>가짜지점</v>
@@ -1131,7 +1131,7 @@
         <v>420000</v>
       </c>
       <c r="F34">
-        <v>4751000</v>
+        <v>5701000</v>
       </c>
       <c r="G34" t="str">
         <v>가짜지점</v>
@@ -1154,7 +1154,7 @@
         <v/>
       </c>
       <c r="F35">
-        <v>4251000</v>
+        <v>5201000</v>
       </c>
       <c r="G35" t="str">
         <v>가짜지점</v>
@@ -1177,7 +1177,7 @@
         <v/>
       </c>
       <c r="F36">
-        <v>4031000</v>
+        <v>4981000</v>
       </c>
       <c r="G36" t="str">
         <v>가짜지점</v>
@@ -1200,7 +1200,7 @@
         <v>1950000</v>
       </c>
       <c r="F37">
-        <v>5981000</v>
+        <v>6931000</v>
       </c>
       <c r="G37" t="str">
         <v>가짜지점</v>
@@ -1223,7 +1223,7 @@
         <v/>
       </c>
       <c r="F38">
-        <v>5401000</v>
+        <v>6351000</v>
       </c>
       <c r="G38" t="str">
         <v>가짜지점</v>
@@ -1246,7 +1246,7 @@
         <v>1050000</v>
       </c>
       <c r="F39">
-        <v>6451000</v>
+        <v>7401000</v>
       </c>
       <c r="G39" t="str">
         <v>가짜지점</v>
@@ -1269,7 +1269,7 @@
         <v/>
       </c>
       <c r="F40">
-        <v>6151000</v>
+        <v>7101000</v>
       </c>
       <c r="G40" t="str">
         <v>가짜지점</v>
@@ -1292,7 +1292,7 @@
         <v/>
       </c>
       <c r="F41">
-        <v>3651000</v>
+        <v>4601000</v>
       </c>
       <c r="G41" t="str">
         <v>가짜지점</v>
@@ -1315,7 +1315,7 @@
         <v>460000</v>
       </c>
       <c r="F42">
-        <v>4111000</v>
+        <v>5061000</v>
       </c>
       <c r="G42" t="str">
         <v>가짜지점</v>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
       <c r="F43">
-        <v>3921000</v>
+        <v>4871000</v>
       </c>
       <c r="G43" t="str">
         <v>가짜지점</v>
@@ -1361,7 +1361,7 @@
         <v/>
       </c>
       <c r="F44">
-        <v>3898000</v>
+        <v>4848000</v>
       </c>
       <c r="G44" t="str">
         <v>가짜지점</v>
@@ -1378,13 +1378,13 @@
         <v>가나식품</v>
       </c>
       <c r="D45">
-        <v>2200000</v>
+        <v>1700000</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45">
-        <v>1698000</v>
+        <v>3148000</v>
       </c>
       <c r="G45" t="str">
         <v>가짜지점</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="F46">
-        <v>1654000</v>
+        <v>3104000</v>
       </c>
       <c r="G46" t="str">
         <v>가짜지점</v>
@@ -1430,7 +1430,7 @@
         <v/>
       </c>
       <c r="F47">
-        <v>1615000</v>
+        <v>3065000</v>
       </c>
       <c r="G47" t="str">
         <v>가짜지점</v>
@@ -1453,7 +1453,7 @@
         <v>1620000</v>
       </c>
       <c r="F48">
-        <v>3235000</v>
+        <v>4685000</v>
       </c>
       <c r="G48" t="str">
         <v>가짜지점</v>
@@ -1476,7 +1476,7 @@
         <v>1590000</v>
       </c>
       <c r="F49">
-        <v>4825000</v>
+        <v>6275000</v>
       </c>
       <c r="G49" t="str">
         <v>가짜지점</v>
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="F50">
-        <v>4693000</v>
+        <v>6143000</v>
       </c>
       <c r="G50" t="str">
         <v>가짜지점</v>
@@ -1522,7 +1522,7 @@
         <v/>
       </c>
       <c r="F51">
-        <v>4645000</v>
+        <v>6095000</v>
       </c>
       <c r="G51" t="str">
         <v>가짜지점</v>
@@ -1545,7 +1545,7 @@
         <v>440000</v>
       </c>
       <c r="F52">
-        <v>5085000</v>
+        <v>6535000</v>
       </c>
       <c r="G52" t="str">
         <v>가짜지점</v>
@@ -1568,7 +1568,7 @@
         <v/>
       </c>
       <c r="F53">
-        <v>4635000</v>
+        <v>6085000</v>
       </c>
       <c r="G53" t="str">
         <v>가짜지점</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F54">
-        <v>4025000</v>
+        <v>5475000</v>
       </c>
       <c r="G54" t="str">
         <v>가짜지점</v>
@@ -1614,7 +1614,7 @@
         <v/>
       </c>
       <c r="F55">
-        <v>3605000</v>
+        <v>5055000</v>
       </c>
       <c r="G55" t="str">
         <v>가짜지점</v>
@@ -1637,7 +1637,7 @@
         <v>1850000</v>
       </c>
       <c r="F56">
-        <v>5455000</v>
+        <v>6905000</v>
       </c>
       <c r="G56" t="str">
         <v>가짜지점</v>
@@ -1660,7 +1660,7 @@
         <v/>
       </c>
       <c r="F57">
-        <v>4535000</v>
+        <v>5985000</v>
       </c>
       <c r="G57" t="str">
         <v>가짜지점</v>
@@ -1683,7 +1683,7 @@
         <v>980000</v>
       </c>
       <c r="F58">
-        <v>5515000</v>
+        <v>6965000</v>
       </c>
       <c r="G58" t="str">
         <v>가짜지점</v>
@@ -1706,7 +1706,7 @@
         <v/>
       </c>
       <c r="F59">
-        <v>5215000</v>
+        <v>6665000</v>
       </c>
       <c r="G59" t="str">
         <v>가짜지점</v>
@@ -1729,7 +1729,7 @@
         <v/>
       </c>
       <c r="F60">
-        <v>4915000</v>
+        <v>6365000</v>
       </c>
       <c r="G60" t="str">
         <v>가짜지점</v>
@@ -1752,7 +1752,7 @@
         <v/>
       </c>
       <c r="F61">
-        <v>4730000</v>
+        <v>6180000</v>
       </c>
       <c r="G61" t="str">
         <v>가짜지점</v>
@@ -1769,13 +1769,13 @@
         <v>가나식품</v>
       </c>
       <c r="D62">
-        <v>2050000</v>
+        <v>1550000</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62">
-        <v>2680000</v>
+        <v>4630000</v>
       </c>
       <c r="G62" t="str">
         <v>가짜지점</v>
@@ -1798,7 +1798,7 @@
         <v/>
       </c>
       <c r="F63">
-        <v>2180000</v>
+        <v>4130000</v>
       </c>
       <c r="G63" t="str">
         <v>가짜지점</v>
@@ -1821,7 +1821,7 @@
         <v/>
       </c>
       <c r="F64">
-        <v>1570000</v>
+        <v>3520000</v>
       </c>
       <c r="G64" t="str">
         <v>가짜지점</v>
@@ -1844,7 +1844,7 @@
         <v/>
       </c>
       <c r="F65">
-        <v>1482000</v>
+        <v>3432000</v>
       </c>
       <c r="G65" t="str">
         <v>가짜지점</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F66">
-        <v>1471000</v>
+        <v>3421000</v>
       </c>
       <c r="G66" t="str">
         <v>가짜지점</v>
@@ -1890,7 +1890,7 @@
         <v>1600000</v>
       </c>
       <c r="F67">
-        <v>3071000</v>
+        <v>5021000</v>
       </c>
       <c r="G67" t="str">
         <v>가짜지점</v>
@@ -1913,7 +1913,7 @@
         <v>1600000</v>
       </c>
       <c r="F68">
-        <v>4671000</v>
+        <v>6621000</v>
       </c>
       <c r="G68" t="str">
         <v>가짜지점</v>
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="F69">
-        <v>4606000</v>
+        <v>6556000</v>
       </c>
       <c r="G69" t="str">
         <v>가짜지점</v>
@@ -1959,7 +1959,7 @@
         <v>430000</v>
       </c>
       <c r="F70">
-        <v>5036000</v>
+        <v>6986000</v>
       </c>
       <c r="G70" t="str">
         <v>가짜지점</v>
@@ -1982,7 +1982,7 @@
         <v/>
       </c>
       <c r="F71">
-        <v>4786000</v>
+        <v>6736000</v>
       </c>
       <c r="G71" t="str">
         <v>가짜지점</v>
@@ -2005,7 +2005,7 @@
         <v/>
       </c>
       <c r="F72">
-        <v>4753000</v>
+        <v>6703000</v>
       </c>
       <c r="G72" t="str">
         <v>가짜지점</v>
@@ -2028,7 +2028,7 @@
         <v>1950000</v>
       </c>
       <c r="F73">
-        <v>6703000</v>
+        <v>8653000</v>
       </c>
       <c r="G73" t="str">
         <v>가짜지점</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="F74">
-        <v>6646000</v>
+        <v>8596000</v>
       </c>
       <c r="G74" t="str">
         <v>가짜지점</v>
@@ -2074,7 +2074,7 @@
         <v>1020000</v>
       </c>
       <c r="F75">
-        <v>7666000</v>
+        <v>9616000</v>
       </c>
       <c r="G75" t="str">
         <v>가짜지점</v>
@@ -2097,7 +2097,7 @@
         <v/>
       </c>
       <c r="F76">
-        <v>7566000</v>
+        <v>9516000</v>
       </c>
       <c r="G76" t="str">
         <v>가짜지점</v>
@@ -2120,7 +2120,7 @@
         <v>470000</v>
       </c>
       <c r="F77">
-        <v>8036000</v>
+        <v>9986000</v>
       </c>
       <c r="G77" t="str">
         <v>가짜지점</v>
@@ -2143,7 +2143,7 @@
         <v/>
       </c>
       <c r="F78">
-        <v>7940000</v>
+        <v>9890000</v>
       </c>
       <c r="G78" t="str">
         <v>가짜지점</v>
